--- a/sources/hwoarang_step8.xlsx
+++ b/sources/hwoarang_step8.xlsx
@@ -425,7 +425,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col hidden="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col hidden="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col hidden="1" min="9" max="9"/>
@@ -6997,27 +6997,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3,3,d+3,4 [F]</t>
+          <t>3,3,d+3,4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>3,3,d+3,4 [F]</t>
+          <t>3,3,d+3,4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Menace to Society [LFF]</t>
+          <t>Menace to Society</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Menace to Society [LFF]</t>
+          <t>Menace to Society</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7161,27 +7161,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3,3,4 [F]</t>
+          <t>3,3,4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3,3,4 [F]</t>
+          <t>3,3,4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Disorderly Conduct [LFF]</t>
+          <t>Disorderly Conduct</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Disorderly Conduct [LFF]</t>
+          <t>Disorderly Conduct</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7325,27 +7325,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3,3,3&lt;4 [F]</t>
+          <t>3,3,3&lt;4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>3,3,3&lt;4 [F]</t>
+          <t>3,3,3&lt;4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Party Hearthy [LFF]</t>
+          <t>Party Hearthy</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Party Hearthy [LFF]</t>
+          <t>Party Hearthy</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RFS</t>
+          <t>RFS; (~F)LFF</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -15034,12 +15034,12 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Y176" t="inlineStr">

--- a/sources/hwoarang_step8.xlsx
+++ b/sources/hwoarang_step8.xlsx
@@ -1027,6 +1027,11 @@
           <t>Can be done from LFF or RFF unless indicated otherwise</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>17408612-fc58-4f13-8e14-136748fa44ab</t>
@@ -1094,6 +1099,11 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>b8fbde6d-1dd0-4a06-832a-6464328e437b</t>
@@ -1161,6 +1171,11 @@
           <t>In RFF 2+5 throws don't work.</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr">
         <is>
           <t>87427b97-ed62-47ff-9c16-7dd832dbaab9</t>
@@ -1226,6 +1241,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>In RFF 2+5 throws don't work.</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>f5efc0a7-f776-4080-ad07-4baaea997c03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -15485,6 +15505,11 @@
           <t>mhhLmmlhmh</t>
         </is>
       </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
+        </is>
+      </c>
       <c r="Z182" t="inlineStr">
         <is>
           <t>43ddfb49-7ac4-4b7a-99bd-30c709526e89</t>
@@ -15530,6 +15555,11 @@
       <c r="S183" t="inlineStr">
         <is>
           <t>mhhLmmlhmh</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>b3e0a845-335b-4f9e-b80f-b2fcded6fdb7</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
